--- a/testdata/TestOutputData.xlsx
+++ b/testdata/TestOutputData.xlsx
@@ -9,9 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
-    <sheet name="home_loan" r:id="rId8" sheetId="24"/>
-    <sheet name="car_loan" r:id="rId9" sheetId="25"/>
-    <sheet name="emi_calculator" r:id="rId10" sheetId="26"/>
+    <sheet name="home_loan" r:id="rId8" sheetId="27"/>
+    <sheet name="car_loan" r:id="rId9" sheetId="28"/>
+    <sheet name="emi_calculator" r:id="rId10" sheetId="29"/>
   </sheets>
   <calcPr calcId="0"/>
   <oleSize ref="A1:N11"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="33">
   <si>
     <t>abc</t>
   </si>
@@ -105,6 +105,27 @@
   </si>
   <si>
     <t>₹ 0.00</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>₹ 15,00,000</t>
+  </si>
+  <si>
+    <t>₹ 78,303</t>
+  </si>
+  <si>
+    <t>₹ 15,78,303</t>
+  </si>
+  <si>
+    <t>₹ 15,00,000.03</t>
+  </si>
+  <si>
+    <t>₹ 78,303.21</t>
+  </si>
+  <si>
+    <t>₹ 15,78,303.24</t>
   </si>
 </sst>
 </file>
@@ -141,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="451">
+  <cellXfs count="487">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1488,6 +1509,114 @@
       <alignment wrapText="true"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1807,11 +1936,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1820,76 +1949,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.49609375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.55078125" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.7734375" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="13.9921875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.4375" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.14453125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.5078125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="7.84765625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.20703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.55078125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.19921875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.37890625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="397" t="s">
+      <c r="A1" s="451" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="398" t="s">
+      <c r="B1" s="452" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="399" t="s">
+      <c r="C1" s="453" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="400" t="s">
+      <c r="D1" s="454" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="401" t="s">
+      <c r="E1" s="455" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="402" t="s">
+      <c r="F1" s="456" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="403" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="404" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="405" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="406" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="407" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="408" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="409" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="410" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="411" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="412" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="413" t="s">
+      <c r="A2" s="457" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="458" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="459" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="460" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="461" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="414" t="s">
+      <c r="F2" s="462" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1898,76 +2007,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.49609375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.55078125" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.7734375" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="13.9921875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.4375" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.14453125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.5078125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="7.84765625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.20703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.55078125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.19921875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.37890625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="415" t="s">
+      <c r="A1" s="463" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="416" t="s">
+      <c r="B1" s="464" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="417" t="s">
+      <c r="C1" s="465" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="418" t="s">
+      <c r="D1" s="466" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="419" t="s">
+      <c r="E1" s="467" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="420" t="s">
+      <c r="F1" s="468" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="421" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="422" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="423" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="424" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="425" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="426" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="427" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="428" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="429" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="430" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="431" t="s">
+      <c r="A2" s="469" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="470" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="471" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="472" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="473" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="432" t="s">
+      <c r="F2" s="474" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1976,76 +2065,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.49609375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="14.3359375" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.55859375" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="14.3359375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.22265625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.14453125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.5078125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="7.84765625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.20703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.55078125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.19921875"/>
+    <col min="6" max="6" width="15.37890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="433" t="s">
+      <c r="A1" s="475" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="434" t="s">
+      <c r="B1" s="476" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="435" t="s">
+      <c r="C1" s="477" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="436" t="s">
+      <c r="D1" s="478" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="437" t="s">
+      <c r="E1" s="479" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="438" t="s">
+      <c r="F1" s="480" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="439" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="440" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="441" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="442" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="443" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="444" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="445" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="446" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="447" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="448" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="449" t="s">
+      <c r="A2" s="481" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="482" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="483" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="484" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="485" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="450" t="s">
+      <c r="F2" s="486" t="s">
         <v>17</v>
       </c>
     </row>

--- a/testdata/TestOutputData.xlsx
+++ b/testdata/TestOutputData.xlsx
@@ -9,9 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
-    <sheet name="home_loan" r:id="rId8" sheetId="27"/>
-    <sheet name="car_loan" r:id="rId9" sheetId="28"/>
-    <sheet name="emi_calculator" r:id="rId10" sheetId="29"/>
+    <sheet name="home_loan" r:id="rId8" sheetId="33"/>
+    <sheet name="car_loan" r:id="rId9" sheetId="34"/>
+    <sheet name="emi_calculator" r:id="rId10" sheetId="35"/>
   </sheets>
   <calcPr calcId="0"/>
   <oleSize ref="A1:N11"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="33">
   <si>
     <t>abc</t>
   </si>
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="487">
+  <cellXfs count="559">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1509,6 +1509,222 @@
       <alignment wrapText="true"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1949,7 +2165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1963,42 +2179,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="451" t="s">
+      <c r="A1" s="523" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="452" t="s">
+      <c r="B1" s="524" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="453" t="s">
+      <c r="C1" s="525" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="454" t="s">
+      <c r="D1" s="526" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="455" t="s">
+      <c r="E1" s="527" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="456" t="s">
+      <c r="F1" s="528" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="457" t="s">
+      <c r="A2" s="529" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="458" t="s">
+      <c r="B2" s="530" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="459" t="s">
+      <c r="C2" s="531" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="460" t="s">
+      <c r="D2" s="532" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="461" t="s">
+      <c r="E2" s="533" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="462" t="s">
+      <c r="F2" s="534" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2007,7 +2223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -2021,42 +2237,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="463" t="s">
+      <c r="A1" s="535" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="464" t="s">
+      <c r="B1" s="536" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="465" t="s">
+      <c r="C1" s="537" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="466" t="s">
+      <c r="D1" s="538" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="467" t="s">
+      <c r="E1" s="539" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="468" t="s">
+      <c r="F1" s="540" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="469" t="s">
+      <c r="A2" s="541" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="470" t="s">
+      <c r="B2" s="542" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="471" t="s">
+      <c r="C2" s="543" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="472" t="s">
+      <c r="D2" s="544" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="473" t="s">
+      <c r="E2" s="545" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="474" t="s">
+      <c r="F2" s="546" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2065,7 +2281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -2079,42 +2295,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="475" t="s">
+      <c r="A1" s="547" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="476" t="s">
+      <c r="B1" s="548" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="477" t="s">
+      <c r="C1" s="549" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="478" t="s">
+      <c r="D1" s="550" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="479" t="s">
+      <c r="E1" s="551" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="480" t="s">
+      <c r="F1" s="552" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="481" t="s">
+      <c r="A2" s="553" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="482" t="s">
+      <c r="B2" s="554" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="483" t="s">
+      <c r="C2" s="555" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="484" t="s">
+      <c r="D2" s="556" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="485" t="s">
+      <c r="E2" s="557" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="486" t="s">
+      <c r="F2" s="558" t="s">
         <v>17</v>
       </c>
     </row>

--- a/testdata/TestOutputData.xlsx
+++ b/testdata/TestOutputData.xlsx
@@ -9,9 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
-    <sheet name="home_loan" r:id="rId8" sheetId="33"/>
-    <sheet name="car_loan" r:id="rId9" sheetId="34"/>
-    <sheet name="emi_calculator" r:id="rId10" sheetId="35"/>
+    <sheet name="home_loan" r:id="rId8" sheetId="39"/>
+    <sheet name="car_loan" r:id="rId9" sheetId="40"/>
+    <sheet name="emi_calculator" r:id="rId10" sheetId="41"/>
   </sheets>
   <calcPr calcId="0"/>
   <oleSize ref="A1:N11"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="33">
   <si>
     <t>abc</t>
   </si>
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="559">
+  <cellXfs count="631">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1509,6 +1509,222 @@
       <alignment wrapText="true"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -2165,7 +2381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -2179,42 +2395,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="523" t="s">
+      <c r="A1" s="595" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="524" t="s">
+      <c r="B1" s="596" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="525" t="s">
+      <c r="C1" s="597" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="526" t="s">
+      <c r="D1" s="598" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="527" t="s">
+      <c r="E1" s="599" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="528" t="s">
+      <c r="F1" s="600" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="529" t="s">
+      <c r="A2" s="601" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="530" t="s">
+      <c r="B2" s="602" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="531" t="s">
+      <c r="C2" s="603" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="532" t="s">
+      <c r="D2" s="604" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="533" t="s">
+      <c r="E2" s="605" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="534" t="s">
+      <c r="F2" s="606" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2223,7 +2439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -2237,42 +2453,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="535" t="s">
+      <c r="A1" s="607" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="536" t="s">
+      <c r="B1" s="608" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="537" t="s">
+      <c r="C1" s="609" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="538" t="s">
+      <c r="D1" s="610" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="539" t="s">
+      <c r="E1" s="611" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="540" t="s">
+      <c r="F1" s="612" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="541" t="s">
+      <c r="A2" s="613" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="542" t="s">
+      <c r="B2" s="614" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="543" t="s">
+      <c r="C2" s="615" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="544" t="s">
+      <c r="D2" s="616" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="545" t="s">
+      <c r="E2" s="617" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="546" t="s">
+      <c r="F2" s="618" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2281,7 +2497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -2295,42 +2511,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="547" t="s">
+      <c r="A1" s="619" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="548" t="s">
+      <c r="B1" s="620" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="549" t="s">
+      <c r="C1" s="621" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="550" t="s">
+      <c r="D1" s="622" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="551" t="s">
+      <c r="E1" s="623" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="552" t="s">
+      <c r="F1" s="624" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="553" t="s">
+      <c r="A2" s="625" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="554" t="s">
+      <c r="B2" s="626" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="555" t="s">
+      <c r="C2" s="627" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="556" t="s">
+      <c r="D2" s="628" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="557" t="s">
+      <c r="E2" s="629" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="558" t="s">
+      <c r="F2" s="630" t="s">
         <v>17</v>
       </c>
     </row>

--- a/testdata/TestOutputData.xlsx
+++ b/testdata/TestOutputData.xlsx
@@ -9,9 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
-    <sheet name="home_loan" r:id="rId8" sheetId="39"/>
-    <sheet name="car_loan" r:id="rId9" sheetId="40"/>
-    <sheet name="emi_calculator" r:id="rId10" sheetId="41"/>
+    <sheet name="home_loan" r:id="rId8" sheetId="53"/>
+    <sheet name="car_loan" r:id="rId9" sheetId="54"/>
+    <sheet name="emi_calculator" r:id="rId10" sheetId="55"/>
   </sheets>
   <calcPr calcId="0"/>
   <oleSize ref="A1:N11"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="86">
   <si>
     <t>abc</t>
   </si>
@@ -126,6 +126,165 @@
   </si>
   <si>
     <t>₹ 15,78,303.24</t>
+  </si>
+  <si>
+    <t>₹ 13,69,508</t>
+  </si>
+  <si>
+    <t>₹ 77,270</t>
+  </si>
+  <si>
+    <t>₹ 14,46,778</t>
+  </si>
+  <si>
+    <t>₹ 1,30,492</t>
+  </si>
+  <si>
+    <t>91.30%</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>₹ 1,033</t>
+  </si>
+  <si>
+    <t>₹ 1,31,525</t>
+  </si>
+  <si>
+    <t>₹ 13,69,507.82</t>
+  </si>
+  <si>
+    <t>₹ 77,270.15</t>
+  </si>
+  <si>
+    <t>₹ 14,46,777.97</t>
+  </si>
+  <si>
+    <t>₹ 1,30,492.18</t>
+  </si>
+  <si>
+    <t>₹ 1,30,492.21</t>
+  </si>
+  <si>
+    <t>₹ 1,033.06</t>
+  </si>
+  <si>
+    <t>₹ 1,31,525.27</t>
+  </si>
+  <si>
+    <t>₹ 8,74,734</t>
+  </si>
+  <si>
+    <t>₹ 1,25,290</t>
+  </si>
+  <si>
+    <t>₹ 10,00,025</t>
+  </si>
+  <si>
+    <t>₹ 11,25,266</t>
+  </si>
+  <si>
+    <t>43.74%</t>
+  </si>
+  <si>
+    <t>₹ 10,34,994</t>
+  </si>
+  <si>
+    <t>₹ 55,943</t>
+  </si>
+  <si>
+    <t>₹ 10,90,936</t>
+  </si>
+  <si>
+    <t>₹ 90,272</t>
+  </si>
+  <si>
+    <t>95.49%</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>₹ 639</t>
+  </si>
+  <si>
+    <t>₹ 90,911</t>
+  </si>
+  <si>
+    <t>₹ 7,30,093</t>
+  </si>
+  <si>
+    <t>₹ 45,615</t>
+  </si>
+  <si>
+    <t>₹ 7,75,708</t>
+  </si>
+  <si>
+    <t>₹ 69,907</t>
+  </si>
+  <si>
+    <t>91.26%</t>
+  </si>
+  <si>
+    <t>₹ 612</t>
+  </si>
+  <si>
+    <t>₹ 70,519</t>
+  </si>
+  <si>
+    <t>₹ 3,31,239.76</t>
+  </si>
+  <si>
+    <t>₹ 91,595.18</t>
+  </si>
+  <si>
+    <t>₹ 4,22,834.94</t>
+  </si>
+  <si>
+    <t>₹ 8,68,760.24</t>
+  </si>
+  <si>
+    <t>27.60%</t>
+  </si>
+  <si>
+    <t>₹ 3,95,676.36</t>
+  </si>
+  <si>
+    <t>₹ 65,598.12</t>
+  </si>
+  <si>
+    <t>₹ 4,61,274.48</t>
+  </si>
+  <si>
+    <t>₹ 4,73,083.88</t>
+  </si>
+  <si>
+    <t>60.58%</t>
+  </si>
+  <si>
+    <t>₹ 4,34,946.28</t>
+  </si>
+  <si>
+    <t>₹ 26,328.20</t>
+  </si>
+  <si>
+    <t>₹ 38,137.60</t>
+  </si>
+  <si>
+    <t>96.82%</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>₹ 38,137.62</t>
+  </si>
+  <si>
+    <t>₹ 301.92</t>
+  </si>
+  <si>
+    <t>₹ 38,439.54</t>
   </si>
 </sst>
 </file>
@@ -162,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="631">
+  <cellXfs count="883">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1509,6 +1668,762 @@
       <alignment wrapText="true"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -2381,56 +3296,96 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.5078125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="7.84765625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.20703125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.9296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.359375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.359375"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="12.55078125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.19921875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.359375"/>
     <col min="6" max="6" bestFit="true" customWidth="true" width="15.37890625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="595" t="s">
+      <c r="A1" s="811" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="596" t="s">
+      <c r="B1" s="812" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="597" t="s">
+      <c r="C1" s="813" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="598" t="s">
+      <c r="D1" s="814" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="599" t="s">
+      <c r="E1" s="815" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="600" t="s">
+      <c r="F1" s="816" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="601" t="s">
+      <c r="A2" s="817" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="602" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="603" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="604" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="605" t="s">
+      <c r="B2" s="818" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="819" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="820" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="821" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="822" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="823" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="824" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="825" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="826" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="827" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="828" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="829" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="830" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="831" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="832" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="833" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="606" t="s">
+      <c r="F4" s="834" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2439,56 +3394,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.5078125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="7.84765625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.20703125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.9296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.359375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.8671875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="12.55078125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.19921875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.8671875"/>
     <col min="6" max="6" bestFit="true" customWidth="true" width="15.37890625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="607" t="s">
+      <c r="A1" s="835" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="608" t="s">
+      <c r="B1" s="836" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="609" t="s">
+      <c r="C1" s="837" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="610" t="s">
+      <c r="D1" s="838" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="611" t="s">
+      <c r="E1" s="839" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="612" t="s">
+      <c r="F1" s="840" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="613" t="s">
+      <c r="A2" s="841" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="614" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="615" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="616" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="617" t="s">
+      <c r="B2" s="842" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="843" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="844" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="845" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="846" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="847" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="848" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="849" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="850" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="851" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="618" t="s">
+      <c r="F3" s="852" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2497,56 +3472,116 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="4.5078125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="7.84765625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.20703125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="4.9296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.859375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.3671875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="12.55078125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.19921875"/>
-    <col min="6" max="6" width="15.37890625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.859375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.37890625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="619" t="s">
+      <c r="A1" s="853" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="620" t="s">
+      <c r="B1" s="854" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="621" t="s">
+      <c r="C1" s="855" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="622" t="s">
+      <c r="D1" s="856" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="623" t="s">
+      <c r="E1" s="857" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="624" t="s">
+      <c r="F1" s="858" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="625" t="s">
+      <c r="A2" s="859" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="626" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="627" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="628" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="629" t="s">
+      <c r="B2" s="860" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="861" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="862" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="863" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="864" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="865" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="866" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="867" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="868" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="869" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="870" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="871" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="872" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="873" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="874" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="875" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="876" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="877" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="878" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="879" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="880" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="881" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="630" t="s">
+      <c r="F5" s="882" t="s">
         <v>17</v>
       </c>
     </row>

--- a/testdata/TestOutputData.xlsx
+++ b/testdata/TestOutputData.xlsx
@@ -9,9 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
-    <sheet name="home_loan" r:id="rId8" sheetId="53"/>
-    <sheet name="car_loan" r:id="rId9" sheetId="54"/>
-    <sheet name="emi_calculator" r:id="rId10" sheetId="55"/>
+    <sheet name="home_loan" r:id="rId8" sheetId="64"/>
+    <sheet name="car_loan" r:id="rId9" sheetId="65"/>
+    <sheet name="emi_calculator" r:id="rId10" sheetId="66"/>
   </sheets>
   <calcPr calcId="0"/>
   <oleSize ref="A1:N11"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="86">
   <si>
     <t>abc</t>
   </si>
@@ -321,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="883">
+  <cellXfs count="1141">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1668,6 +1668,780 @@
       <alignment wrapText="true"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -3296,7 +4070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -3310,82 +4084,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="811" t="s">
+      <c r="A1" s="1069" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="812" t="s">
+      <c r="B1" s="1070" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="813" t="s">
+      <c r="C1" s="1071" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="814" t="s">
+      <c r="D1" s="1072" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="815" t="s">
+      <c r="E1" s="1073" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="816" t="s">
+      <c r="F1" s="1074" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="817" t="s">
+      <c r="A2" s="1075" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="818" t="s">
+      <c r="B2" s="1076" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="819" t="s">
+      <c r="C2" s="1077" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="820" t="s">
+      <c r="D2" s="1078" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="821" t="s">
+      <c r="E2" s="1079" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="822" t="s">
+      <c r="F2" s="1080" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="823" t="s">
+      <c r="A3" s="1081" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="824" t="s">
+      <c r="B3" s="1082" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="825" t="s">
+      <c r="C3" s="1083" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="826" t="s">
+      <c r="D3" s="1084" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="827" t="s">
+      <c r="E3" s="1085" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="828" t="s">
+      <c r="F3" s="1086" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="829" t="s">
+      <c r="A4" s="1087" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="830" t="s">
+      <c r="B4" s="1088" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="831" t="s">
+      <c r="C4" s="1089" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="832" t="s">
+      <c r="D4" s="1090" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="833" t="s">
+      <c r="E4" s="1091" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="834" t="s">
+      <c r="F4" s="1092" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3394,7 +4168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -3408,62 +4182,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="835" t="s">
+      <c r="A1" s="1093" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="836" t="s">
+      <c r="B1" s="1094" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="837" t="s">
+      <c r="C1" s="1095" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="838" t="s">
+      <c r="D1" s="1096" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="839" t="s">
+      <c r="E1" s="1097" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="840" t="s">
+      <c r="F1" s="1098" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="841" t="s">
+      <c r="A2" s="1099" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="842" t="s">
+      <c r="B2" s="1100" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="843" t="s">
+      <c r="C2" s="1101" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="844" t="s">
+      <c r="D2" s="1102" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="845" t="s">
+      <c r="E2" s="1103" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="846" t="s">
+      <c r="F2" s="1104" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="847" t="s">
+      <c r="A3" s="1105" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="848" t="s">
+      <c r="B3" s="1106" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="849" t="s">
+      <c r="C3" s="1107" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="850" t="s">
+      <c r="D3" s="1108" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="851" t="s">
+      <c r="E3" s="1109" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="852" t="s">
+      <c r="F3" s="1110" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3472,7 +4246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -3486,102 +4260,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="853" t="s">
+      <c r="A1" s="1111" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="854" t="s">
+      <c r="B1" s="1112" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="855" t="s">
+      <c r="C1" s="1113" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="856" t="s">
+      <c r="D1" s="1114" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="857" t="s">
+      <c r="E1" s="1115" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="858" t="s">
+      <c r="F1" s="1116" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="859" t="s">
+      <c r="A2" s="1117" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="860" t="s">
+      <c r="B2" s="1118" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="861" t="s">
+      <c r="C2" s="1119" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="862" t="s">
+      <c r="D2" s="1120" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="863" t="s">
+      <c r="E2" s="1121" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="864" t="s">
+      <c r="F2" s="1122" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="865" t="s">
+      <c r="A3" s="1123" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="866" t="s">
+      <c r="B3" s="1124" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="867" t="s">
+      <c r="C3" s="1125" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="868" t="s">
+      <c r="D3" s="1126" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="869" t="s">
+      <c r="E3" s="1127" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="870" t="s">
+      <c r="F3" s="1128" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="871" t="s">
+      <c r="A4" s="1129" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="872" t="s">
+      <c r="B4" s="1130" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="873" t="s">
+      <c r="C4" s="1131" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="874" t="s">
+      <c r="D4" s="1132" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="875" t="s">
+      <c r="E4" s="1133" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="876" t="s">
+      <c r="F4" s="1134" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="877" t="s">
+      <c r="A5" s="1135" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="878" t="s">
+      <c r="B5" s="1136" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="879" t="s">
+      <c r="C5" s="1137" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="880" t="s">
+      <c r="D5" s="1138" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="881" t="s">
+      <c r="E5" s="1139" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="882" t="s">
+      <c r="F5" s="1140" t="s">
         <v>17</v>
       </c>
     </row>
